--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/65.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/65.xlsx
@@ -426,13 +426,13 @@
         <v>-5.532947292708424</v>
       </c>
       <c r="E2">
-        <v>-4.227047269005397</v>
+        <v>-6.594691976805729</v>
       </c>
       <c r="F2">
-        <v>-5.040354857550618</v>
+        <v>-4.926086544538842</v>
       </c>
       <c r="G2">
-        <v>-8.749243323675797</v>
+        <v>-13.06238095842419</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.296416491335024</v>
       </c>
       <c r="E3">
-        <v>-4.089635253716648</v>
+        <v>-6.451306904300862</v>
       </c>
       <c r="F3">
-        <v>-4.972837115650639</v>
+        <v>-5.040212378357336</v>
       </c>
       <c r="G3">
-        <v>-8.393359678204146</v>
+        <v>-12.61440455714109</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.169538079463491</v>
       </c>
       <c r="E4">
-        <v>-4.867310095053878</v>
+        <v>-7.559342981445661</v>
       </c>
       <c r="F4">
-        <v>-4.802175206591079</v>
+        <v>-5.211662893184361</v>
       </c>
       <c r="G4">
-        <v>-8.485055168550879</v>
+        <v>-12.25663059016651</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.160434153403886</v>
       </c>
       <c r="E5">
-        <v>-6.146431920208463</v>
+        <v>-8.137846478977533</v>
       </c>
       <c r="F5">
-        <v>-5.167111637526998</v>
+        <v>-4.905290380891561</v>
       </c>
       <c r="G5">
-        <v>-8.538944228839135</v>
+        <v>-11.78824136508827</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.230555557229224</v>
       </c>
       <c r="E6">
-        <v>-6.49391984471304</v>
+        <v>-9.905826130208148</v>
       </c>
       <c r="F6">
-        <v>-4.991137408313285</v>
+        <v>-4.928823470437692</v>
       </c>
       <c r="G6">
-        <v>-8.563094658548119</v>
+        <v>-12.23613831327842</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.347478360754899</v>
       </c>
       <c r="E7">
-        <v>-6.994352450352676</v>
+        <v>-9.218430946687834</v>
       </c>
       <c r="F7">
-        <v>-4.489816911445649</v>
+        <v>-4.539251392942515</v>
       </c>
       <c r="G7">
-        <v>-8.478632710204693</v>
+        <v>-11.90938084746128</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.477707596584285</v>
       </c>
       <c r="E8">
-        <v>-7.930446897900238</v>
+        <v>-9.651325890977075</v>
       </c>
       <c r="F8">
-        <v>-4.30883437291461</v>
+        <v>-4.318265335795483</v>
       </c>
       <c r="G8">
-        <v>-8.49758558341702</v>
+        <v>-12.01022668567856</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.594394349675186</v>
       </c>
       <c r="E9">
-        <v>-7.709212828729511</v>
+        <v>-9.933816628049559</v>
       </c>
       <c r="F9">
-        <v>-4.65579191774017</v>
+        <v>-4.165448945694433</v>
       </c>
       <c r="G9">
-        <v>-8.824412570690489</v>
+        <v>-12.32182847401692</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.675506913078797</v>
       </c>
       <c r="E10">
-        <v>-8.202866308779665</v>
+        <v>-9.833071666800917</v>
       </c>
       <c r="F10">
-        <v>-3.540268469658007</v>
+        <v>-3.833461656572267</v>
       </c>
       <c r="G10">
-        <v>-9.786145913122004</v>
+        <v>-12.62124745477076</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.710877363023314</v>
       </c>
       <c r="E11">
-        <v>-8.864349564028089</v>
+        <v>-10.11947047694202</v>
       </c>
       <c r="F11">
-        <v>-3.375091181172383</v>
+        <v>-3.629917703458581</v>
       </c>
       <c r="G11">
-        <v>-11.05965650280546</v>
+        <v>-12.58109384792494</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.697767743207594</v>
       </c>
       <c r="E12">
-        <v>-9.832165971999382</v>
+        <v>-10.38129778711751</v>
       </c>
       <c r="F12">
-        <v>-3.447519485036157</v>
+        <v>-3.374198201112165</v>
       </c>
       <c r="G12">
-        <v>-10.35092498212167</v>
+        <v>-13.48651812127899</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.641492326645766</v>
       </c>
       <c r="E13">
-        <v>-10.44503605877547</v>
+        <v>-11.04842804945349</v>
       </c>
       <c r="F13">
-        <v>-3.21725571297777</v>
+        <v>-2.963125847677327</v>
       </c>
       <c r="G13">
-        <v>-10.08550861460168</v>
+        <v>-12.80940231049524</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.556671325003455</v>
       </c>
       <c r="E14">
-        <v>-10.64391305177032</v>
+        <v>-10.86664151736358</v>
       </c>
       <c r="F14">
-        <v>-3.015774394697055</v>
+        <v>-2.643810923083187</v>
       </c>
       <c r="G14">
-        <v>-10.2088827152137</v>
+        <v>-12.12697638466649</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.457249628888975</v>
       </c>
       <c r="E15">
-        <v>-10.93621699201743</v>
+        <v>-13.07013809933388</v>
       </c>
       <c r="F15">
-        <v>-2.235921157209905</v>
+        <v>-2.356136319806378</v>
       </c>
       <c r="G15">
-        <v>-9.123685887440605</v>
+        <v>-12.12335133730099</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.360369427945725</v>
       </c>
       <c r="E16">
-        <v>-11.61858556938923</v>
+        <v>-12.5954770392719</v>
       </c>
       <c r="F16">
-        <v>-2.066898587240486</v>
+        <v>-2.028750611606763</v>
       </c>
       <c r="G16">
-        <v>-9.716833021166284</v>
+        <v>-12.34821352196491</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.279820761455733</v>
       </c>
       <c r="E17">
-        <v>-11.66734817750383</v>
+        <v>-13.38195070560603</v>
       </c>
       <c r="F17">
-        <v>-1.853873140834357</v>
+        <v>-1.807063755636962</v>
       </c>
       <c r="G17">
-        <v>-8.278950534912472</v>
+        <v>-11.58490765806623</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.223611447841902</v>
       </c>
       <c r="E18">
-        <v>-13.47174581670413</v>
+        <v>-13.67527355250486</v>
       </c>
       <c r="F18">
-        <v>-1.389172281742279</v>
+        <v>-1.166715044087874</v>
       </c>
       <c r="G18">
-        <v>-8.966901761246261</v>
+        <v>-11.26271874509328</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.198074816898129</v>
       </c>
       <c r="E19">
-        <v>-13.13167100415011</v>
+        <v>-15.65722812907191</v>
       </c>
       <c r="F19">
-        <v>-1.20901231204222</v>
+        <v>-1.182338053304673</v>
       </c>
       <c r="G19">
-        <v>-8.082770916800801</v>
+        <v>-11.67068720353429</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.20712508708183</v>
       </c>
       <c r="E20">
-        <v>-15.54908364129473</v>
+        <v>-15.35845752794185</v>
       </c>
       <c r="F20">
-        <v>-1.206419522071457</v>
+        <v>-0.7311412396130326</v>
       </c>
       <c r="G20">
-        <v>-8.380514761511773</v>
+        <v>-11.22546186559432</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.260030529403072</v>
       </c>
       <c r="E21">
-        <v>-15.80069924258292</v>
+        <v>-16.7413493349822</v>
       </c>
       <c r="F21">
-        <v>-0.862537705412493</v>
+        <v>-0.7602699509650744</v>
       </c>
       <c r="G21">
-        <v>-7.195759897736176</v>
+        <v>-9.962733722732269</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.369940592451742</v>
       </c>
       <c r="E22">
-        <v>-16.49619133762895</v>
+        <v>-16.5939882622986</v>
       </c>
       <c r="F22">
-        <v>-0.493972196884909</v>
+        <v>-0.47204945356982</v>
       </c>
       <c r="G22">
-        <v>-7.761833390041695</v>
+        <v>-10.68426050192535</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.540228865217415</v>
       </c>
       <c r="E23">
-        <v>-17.41873206247156</v>
+        <v>-17.1168368142762</v>
       </c>
       <c r="F23">
-        <v>0.02659210311716198</v>
+        <v>-0.2602806405137376</v>
       </c>
       <c r="G23">
-        <v>-7.356327977481906</v>
+        <v>-10.57656845553285</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.7668783500648</v>
       </c>
       <c r="E24">
-        <v>-16.70940547933209</v>
+        <v>-18.40850704090604</v>
       </c>
       <c r="F24">
-        <v>-0.2754579880678302</v>
+        <v>-0.4865243455663386</v>
       </c>
       <c r="G24">
-        <v>-7.397332394531319</v>
+        <v>-10.22326703558183</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.037361237243719</v>
       </c>
       <c r="E25">
-        <v>-17.67518860247394</v>
+        <v>-18.27372154054174</v>
       </c>
       <c r="F25">
-        <v>-0.2881402930046906</v>
+        <v>-0.1545345713419639</v>
       </c>
       <c r="G25">
-        <v>-6.248924010231381</v>
+        <v>-10.3468728743816</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.330663001996267</v>
       </c>
       <c r="E26">
-        <v>-18.15056063295513</v>
+        <v>-18.16114367671106</v>
       </c>
       <c r="F26">
-        <v>-0.2867941959751414</v>
+        <v>-0.1459808495406562</v>
       </c>
       <c r="G26">
-        <v>-6.943152030907627</v>
+        <v>-9.766441546072263</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.620403230074498</v>
       </c>
       <c r="E27">
-        <v>-18.08837109940779</v>
+        <v>-18.70723688577003</v>
       </c>
       <c r="F27">
-        <v>-0.09000475066388243</v>
+        <v>-0.2000831813522976</v>
       </c>
       <c r="G27">
-        <v>-6.651840576179459</v>
+        <v>-9.457809317082628</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.878112686594874</v>
       </c>
       <c r="E28">
-        <v>-17.76177755397461</v>
+        <v>-18.26025385884293</v>
       </c>
       <c r="F28">
-        <v>-0.4173763766176499</v>
+        <v>-0.1031807625728114</v>
       </c>
       <c r="G28">
-        <v>-7.008032102386264</v>
+        <v>-10.16349844641583</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.077995312276291</v>
       </c>
       <c r="E29">
-        <v>-18.70829654868783</v>
+        <v>-18.77590666562235</v>
       </c>
       <c r="F29">
-        <v>-0.6151201011769338</v>
+        <v>-0.2822936758757317</v>
       </c>
       <c r="G29">
-        <v>-6.53436917826396</v>
+        <v>-10.39915632008331</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.201182137650685</v>
       </c>
       <c r="E30">
-        <v>-18.43287475954132</v>
+        <v>-19.10259078053569</v>
       </c>
       <c r="F30">
-        <v>-0.5176941541988784</v>
+        <v>-0.4544118548294129</v>
       </c>
       <c r="G30">
-        <v>-6.471535023928593</v>
+        <v>-10.22181701663563</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.236194167966405</v>
       </c>
       <c r="E31">
-        <v>-18.3508595667884</v>
+        <v>-19.632943013944</v>
       </c>
       <c r="F31">
-        <v>-0.6128835091893752</v>
+        <v>-0.5535326415135962</v>
       </c>
       <c r="G31">
-        <v>-6.679222098334771</v>
+        <v>-9.742241458180191</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.178071259396111</v>
       </c>
       <c r="E32">
-        <v>-17.61693884131328</v>
+        <v>-18.53804403989545</v>
       </c>
       <c r="F32">
-        <v>-0.8702158428690416</v>
+        <v>-0.5994092850154384</v>
       </c>
       <c r="G32">
-        <v>-6.869998906126352</v>
+        <v>-9.888984699753925</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.028775937744036</v>
       </c>
       <c r="E33">
-        <v>-18.13102026761203</v>
+        <v>-17.58219638872643</v>
       </c>
       <c r="F33">
-        <v>-1.153536547076737</v>
+        <v>-0.537428350835771</v>
       </c>
       <c r="G33">
-        <v>-5.13004569214174</v>
+        <v>-9.378184075772078</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.794368102328649</v>
       </c>
       <c r="E34">
-        <v>-18.12673180272677</v>
+        <v>-18.67355862457499</v>
       </c>
       <c r="F34">
-        <v>-0.9009938337200573</v>
+        <v>-0.9011578504658115</v>
       </c>
       <c r="G34">
-        <v>-6.461596766219701</v>
+        <v>-9.206720990656605</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.485214726665655</v>
       </c>
       <c r="E35">
-        <v>-18.28512423809305</v>
+        <v>-18.85356546637988</v>
       </c>
       <c r="F35">
-        <v>-0.7436570427019303</v>
+        <v>-1.033263398762068</v>
       </c>
       <c r="G35">
-        <v>-6.309397745597248</v>
+        <v>-9.453167932236569</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.120738535139449</v>
       </c>
       <c r="E36">
-        <v>-18.70005472599387</v>
+        <v>-18.66147665592252</v>
       </c>
       <c r="F36">
-        <v>-0.8964833732118139</v>
+        <v>-1.140894003775211</v>
       </c>
       <c r="G36">
-        <v>-5.37737654938069</v>
+        <v>-9.629706083663745</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.72252403998136</v>
       </c>
       <c r="E37">
-        <v>-16.60633288244351</v>
+        <v>-17.95879334415232</v>
       </c>
       <c r="F37">
-        <v>-0.8089845811889077</v>
+        <v>-0.7868704850037721</v>
       </c>
       <c r="G37">
-        <v>-5.47349823911343</v>
+        <v>-8.436340490940504</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.314162705857816</v>
       </c>
       <c r="E38">
-        <v>-16.94988103456141</v>
+        <v>-18.36930856989565</v>
       </c>
       <c r="F38">
-        <v>-1.152878823358914</v>
+        <v>-0.9491095543116665</v>
       </c>
       <c r="G38">
-        <v>-5.407889847616153</v>
+        <v>-8.775697893080114</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.919250149081792</v>
       </c>
       <c r="E39">
-        <v>-15.95741614256637</v>
+        <v>-17.98072927224547</v>
       </c>
       <c r="F39">
-        <v>-1.139450159392131</v>
+        <v>-0.8740677512920593</v>
       </c>
       <c r="G39">
-        <v>-5.204486619137792</v>
+        <v>-8.09908197467279</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.553810359415764</v>
       </c>
       <c r="E40">
-        <v>-16.84949835123338</v>
+        <v>-16.5134584090202</v>
       </c>
       <c r="F40">
-        <v>-1.06651406631044</v>
+        <v>-1.11885528902373</v>
       </c>
       <c r="G40">
-        <v>-4.869830191663946</v>
+        <v>-7.789824052576233</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.229508561054251</v>
       </c>
       <c r="E41">
-        <v>-14.97040353327656</v>
+        <v>-16.95731678888201</v>
       </c>
       <c r="F41">
-        <v>-1.007854885415999</v>
+        <v>-1.255509402728759</v>
       </c>
       <c r="G41">
-        <v>-4.641720361826004</v>
+        <v>-7.809938927272845</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.950717283861756</v>
       </c>
       <c r="E42">
-        <v>-16.26180205146594</v>
+        <v>-16.64765973623751</v>
       </c>
       <c r="F42">
-        <v>-1.178790984085885</v>
+        <v>-1.159140452556676</v>
       </c>
       <c r="G42">
-        <v>-4.888544705597447</v>
+        <v>-7.652449654878636</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.710845800405571</v>
       </c>
       <c r="E43">
-        <v>-15.29353279609388</v>
+        <v>-17.48643274888623</v>
       </c>
       <c r="F43">
-        <v>-0.9940600830571789</v>
+        <v>-1.172045588324889</v>
       </c>
       <c r="G43">
-        <v>-4.741086386187229</v>
+        <v>-7.900363168132498</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.503913621799867</v>
       </c>
       <c r="E44">
-        <v>-13.97772580300316</v>
+        <v>-16.67742539588993</v>
       </c>
       <c r="F44">
-        <v>-1.751526691483672</v>
+        <v>-1.216512350507166</v>
       </c>
       <c r="G44">
-        <v>-4.830699543389761</v>
+        <v>-7.045937848810919</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.317511514157404</v>
       </c>
       <c r="E45">
-        <v>-14.03654615188879</v>
+        <v>-16.52159607681198</v>
       </c>
       <c r="F45">
-        <v>-1.094533593710134</v>
+        <v>-1.485795540707021</v>
       </c>
       <c r="G45">
-        <v>-4.555947437449027</v>
+        <v>-7.580564469038901</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.135342180438029</v>
       </c>
       <c r="E46">
-        <v>-14.46244460383618</v>
+        <v>-15.58634392542984</v>
       </c>
       <c r="F46">
-        <v>-1.58534707844066</v>
+        <v>-1.358145780670423</v>
       </c>
       <c r="G46">
-        <v>-4.959138778676865</v>
+        <v>-7.403526425235296</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.946457619079292</v>
       </c>
       <c r="E47">
-        <v>-13.96501437646363</v>
+        <v>-15.68274155163112</v>
       </c>
       <c r="F47">
-        <v>-1.515363286782547</v>
+        <v>-1.554208747769427</v>
       </c>
       <c r="G47">
-        <v>-4.726056509438938</v>
+        <v>-7.520802500963978</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.740019871339844</v>
       </c>
       <c r="E48">
-        <v>-14.73529874822034</v>
+        <v>-16.06571459845981</v>
       </c>
       <c r="F48">
-        <v>-1.79045747431304</v>
+        <v>-1.540714642777823</v>
       </c>
       <c r="G48">
-        <v>-4.874971468886435</v>
+        <v>-7.617109581246916</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.507415707716439</v>
       </c>
       <c r="E49">
-        <v>-12.70690014223062</v>
+        <v>-15.27582646272389</v>
       </c>
       <c r="F49">
-        <v>-2.179424015236771</v>
+        <v>-1.553794564068027</v>
       </c>
       <c r="G49">
-        <v>-4.37923713765381</v>
+        <v>-7.169513892700834</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.247569009750555</v>
       </c>
       <c r="E50">
-        <v>-12.74992970225151</v>
+        <v>-14.95459915898979</v>
       </c>
       <c r="F50">
-        <v>-1.674549822211125</v>
+        <v>-1.738146072826252</v>
       </c>
       <c r="G50">
-        <v>-4.186371375626949</v>
+        <v>-7.266221548994023</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.961187478329866</v>
       </c>
       <c r="E51">
-        <v>-13.62397047047196</v>
+        <v>-15.62419743965996</v>
       </c>
       <c r="F51">
-        <v>-2.127656022766218</v>
+        <v>-1.98776796272066</v>
       </c>
       <c r="G51">
-        <v>-5.149571289732362</v>
+        <v>-6.364541502644887</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.657183910192412</v>
       </c>
       <c r="E52">
-        <v>-13.39850227810406</v>
+        <v>-14.33524429743473</v>
       </c>
       <c r="F52">
-        <v>-1.713562613413371</v>
+        <v>-2.204086169552918</v>
       </c>
       <c r="G52">
-        <v>-3.931985745843812</v>
+        <v>-6.991138388499363</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.347915918567015</v>
       </c>
       <c r="E53">
-        <v>-12.66864359381383</v>
+        <v>-13.97951455023619</v>
       </c>
       <c r="F53">
-        <v>-2.390458894773973</v>
+        <v>-2.396772711118111</v>
       </c>
       <c r="G53">
-        <v>-4.652694820288689</v>
+        <v>-6.272260045737703</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.044854074939043</v>
       </c>
       <c r="E54">
-        <v>-12.39118851983787</v>
+        <v>-13.74600831650467</v>
       </c>
       <c r="F54">
-        <v>-2.038424286136656</v>
+        <v>-2.100378712559433</v>
       </c>
       <c r="G54">
-        <v>-4.103352825138646</v>
+        <v>-7.0599215931688</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.7634038021256857</v>
       </c>
       <c r="E55">
-        <v>-12.24466521484569</v>
+        <v>-13.55979293683526</v>
       </c>
       <c r="F55">
-        <v>-1.930744807446748</v>
+        <v>-2.248780732770965</v>
       </c>
       <c r="G55">
-        <v>-4.274885431710443</v>
+        <v>-6.377416214247113</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.5152752947574633</v>
       </c>
       <c r="E56">
-        <v>-12.40347879829469</v>
+        <v>-13.88700235473349</v>
       </c>
       <c r="F56">
-        <v>-2.03117027279034</v>
+        <v>-2.413730220220819</v>
       </c>
       <c r="G56">
-        <v>-3.927784663554477</v>
+        <v>-6.50633878918295</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.3085611463394722</v>
       </c>
       <c r="E57">
-        <v>-12.38368936688117</v>
+        <v>-13.56329344724319</v>
       </c>
       <c r="F57">
-        <v>-2.143077738704137</v>
+        <v>-2.035334475724214</v>
       </c>
       <c r="G57">
-        <v>-4.303425644804499</v>
+        <v>-5.69961512053673</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.1498554318997137</v>
       </c>
       <c r="E58">
-        <v>-11.57666095702622</v>
+        <v>-13.69358670139188</v>
       </c>
       <c r="F58">
-        <v>-2.014936756797678</v>
+        <v>-2.299786627230942</v>
       </c>
       <c r="G58">
-        <v>-5.546072018425333</v>
+        <v>-6.028560856955333</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.03998547193316387</v>
       </c>
       <c r="E59">
-        <v>-11.49666999215473</v>
+        <v>-13.42594935906456</v>
       </c>
       <c r="F59">
-        <v>-2.089120371187985</v>
+        <v>-2.249866722436035</v>
       </c>
       <c r="G59">
-        <v>-4.592118458011105</v>
+        <v>-6.867251153328756</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.02274367847929808</v>
       </c>
       <c r="E60">
-        <v>-10.79775889923291</v>
+        <v>-12.93063845752759</v>
       </c>
       <c r="F60">
-        <v>-1.963709688241154</v>
+        <v>-2.248472580097123</v>
       </c>
       <c r="G60">
-        <v>-4.71142058760982</v>
+        <v>-6.372079614837808</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.04356946925286555</v>
       </c>
       <c r="E61">
-        <v>-11.28273582308437</v>
+        <v>-13.08917127558812</v>
       </c>
       <c r="F61">
-        <v>-1.960050789422989</v>
+        <v>-1.964850350154809</v>
       </c>
       <c r="G61">
-        <v>-4.474180273174568</v>
+        <v>-6.856097925406952</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.03172755279771344</v>
       </c>
       <c r="E62">
-        <v>-12.00990459381405</v>
+        <v>-12.99065432355125</v>
       </c>
       <c r="F62">
-        <v>-1.932311250205442</v>
+        <v>-2.48632585429996</v>
       </c>
       <c r="G62">
-        <v>-4.572311464049645</v>
+        <v>-7.096645474835936</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.001992548295955956</v>
       </c>
       <c r="E63">
-        <v>-11.05784727538945</v>
+        <v>-12.96968296042173</v>
       </c>
       <c r="F63">
-        <v>-2.153499428998757</v>
+        <v>-2.328327197726996</v>
       </c>
       <c r="G63">
-        <v>-4.504362516856104</v>
+        <v>-7.503316199425547</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.04730203814690432</v>
       </c>
       <c r="E64">
-        <v>-10.07970141820666</v>
+        <v>-13.16138685058844</v>
       </c>
       <c r="F64">
-        <v>-1.939111318215023</v>
+        <v>-2.17360639096691</v>
       </c>
       <c r="G64">
-        <v>-3.902598033091702</v>
+        <v>-6.039369788141054</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.09524903181421536</v>
       </c>
       <c r="E65">
-        <v>-10.78182772767392</v>
+        <v>-13.27329902874</v>
       </c>
       <c r="F65">
-        <v>-1.958195246440718</v>
+        <v>-2.182296793389679</v>
       </c>
       <c r="G65">
-        <v>-4.009839845290852</v>
+        <v>-7.530691100489781</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.1394305770625174</v>
       </c>
       <c r="E66">
-        <v>-9.878487732623842</v>
+        <v>-12.01723166475846</v>
       </c>
       <c r="F66">
-        <v>-2.177974372281871</v>
+        <v>-2.021442754379266</v>
       </c>
       <c r="G66">
-        <v>-4.823532212297239</v>
+        <v>-7.227554377095336</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.1768466797371533</v>
       </c>
       <c r="E67">
-        <v>-11.24816545250981</v>
+        <v>-11.88762221018493</v>
       </c>
       <c r="F67">
-        <v>-2.31873553156998</v>
+        <v>-2.741367752110885</v>
       </c>
       <c r="G67">
-        <v>-5.319925342092178</v>
+        <v>-8.152315546944271</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.2082172435898565</v>
       </c>
       <c r="E68">
-        <v>-10.27310348612625</v>
+        <v>-12.8005218138652</v>
       </c>
       <c r="F68">
-        <v>-1.919562675876357</v>
+        <v>-2.52857424857754</v>
       </c>
       <c r="G68">
-        <v>-4.909404453040394</v>
+        <v>-7.764577832293751</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.2355607052657743</v>
       </c>
       <c r="E69">
-        <v>-8.958252001051141</v>
+        <v>-11.23905416280638</v>
       </c>
       <c r="F69">
-        <v>-2.026114746531055</v>
+        <v>-2.308188757797537</v>
       </c>
       <c r="G69">
-        <v>-5.006664970438642</v>
+        <v>-7.211246629768886</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.2604996415674022</v>
       </c>
       <c r="E70">
-        <v>-9.92529856844113</v>
+        <v>-12.64084329188074</v>
       </c>
       <c r="F70">
-        <v>-1.919308367083698</v>
+        <v>-2.13196187652597</v>
       </c>
       <c r="G70">
-        <v>-4.783653380731178</v>
+        <v>-7.365527983535541</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.28398196632796</v>
       </c>
       <c r="E71">
-        <v>-10.93677399432037</v>
+        <v>-12.51435395589849</v>
       </c>
       <c r="F71">
-        <v>-1.947902781460934</v>
+        <v>-2.637226230598334</v>
       </c>
       <c r="G71">
-        <v>-5.034778123158134</v>
+        <v>-7.673561003782568</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.3054934061594912</v>
       </c>
       <c r="E72">
-        <v>-9.638478610217314</v>
+        <v>-12.4875589751951</v>
       </c>
       <c r="F72">
-        <v>-2.571460485755276</v>
+        <v>-2.610234707145515</v>
       </c>
       <c r="G72">
-        <v>-4.768501013797934</v>
+        <v>-7.393240560244781</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.32278418704699</v>
       </c>
       <c r="E73">
-        <v>-10.27751874828372</v>
+        <v>-12.52106515437786</v>
       </c>
       <c r="F73">
-        <v>-2.32483977096121</v>
+        <v>-2.073038446430036</v>
       </c>
       <c r="G73">
-        <v>-4.334399108869921</v>
+        <v>-7.640601212393584</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.3322453650590943</v>
       </c>
       <c r="E74">
-        <v>-10.12794778028438</v>
+        <v>-13.68139604936323</v>
       </c>
       <c r="F74">
-        <v>-2.186693767563739</v>
+        <v>-2.57967292018663</v>
       </c>
       <c r="G74">
-        <v>-3.745585479255148</v>
+        <v>-6.965862373307028</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.329739073482627</v>
       </c>
       <c r="E75">
-        <v>-10.62162390270457</v>
+        <v>-11.921907286897</v>
       </c>
       <c r="F75">
-        <v>-2.518966843439871</v>
+        <v>-2.849180597952644</v>
       </c>
       <c r="G75">
-        <v>-3.448695755293308</v>
+        <v>-6.478665939020183</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.3109384584456998</v>
       </c>
       <c r="E76">
-        <v>-9.789734170547511</v>
+        <v>-13.21412093040776</v>
       </c>
       <c r="F76">
-        <v>-2.672764020545836</v>
+        <v>-2.412544826467413</v>
       </c>
       <c r="G76">
-        <v>-4.216507271670935</v>
+        <v>-6.465009938670689</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.2730257833782675</v>
       </c>
       <c r="E77">
-        <v>-10.83903141133882</v>
+        <v>-14.25768965157936</v>
       </c>
       <c r="F77">
-        <v>-2.397841305067722</v>
+        <v>-2.755570111231883</v>
       </c>
       <c r="G77">
-        <v>-3.920815965194311</v>
+        <v>-6.719610753913879</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.2149113389007828</v>
       </c>
       <c r="E78">
-        <v>-12.24977333352634</v>
+        <v>-14.19266982177723</v>
       </c>
       <c r="F78">
-        <v>-3.218251410595935</v>
+        <v>-2.877747676205587</v>
       </c>
       <c r="G78">
-        <v>-3.770126553337765</v>
+        <v>-6.168593622720965</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.1377262995439664</v>
       </c>
       <c r="E79">
-        <v>-12.6190386895338</v>
+        <v>-15.44282752717876</v>
       </c>
       <c r="F79">
-        <v>-2.85078928744888</v>
+        <v>-2.564877450005228</v>
       </c>
       <c r="G79">
-        <v>-3.366610778647078</v>
+        <v>-6.63461911828417</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.04543764198695541</v>
       </c>
       <c r="E80">
-        <v>-12.44239650391661</v>
+        <v>-14.91346250110411</v>
       </c>
       <c r="F80">
-        <v>-2.944495036420963</v>
+        <v>-3.244872653819703</v>
       </c>
       <c r="G80">
-        <v>-2.932919381365935</v>
+        <v>-6.529976084333347</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.05455931305897621</v>
       </c>
       <c r="E81">
-        <v>-12.86153394417054</v>
+        <v>-16.03704482951725</v>
       </c>
       <c r="F81">
-        <v>-3.068615122954233</v>
+        <v>-3.228182707388099</v>
       </c>
       <c r="G81">
-        <v>-2.571679273211742</v>
+        <v>-6.518021704391039</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.1546766312204964</v>
       </c>
       <c r="E82">
-        <v>-13.08590171735458</v>
+        <v>-16.50601812622559</v>
       </c>
       <c r="F82">
-        <v>-2.886576415984625</v>
+        <v>-2.919344973704567</v>
       </c>
       <c r="G82">
-        <v>-3.074683562448606</v>
+        <v>-5.647156215921439</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.2456367718798594</v>
       </c>
       <c r="E83">
-        <v>-13.47742905158375</v>
+        <v>-16.97537181475059</v>
       </c>
       <c r="F83">
-        <v>-3.260703583254605</v>
+        <v>-3.371570619710485</v>
       </c>
       <c r="G83">
-        <v>-2.871800089619911</v>
+        <v>-5.114549028472412</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.3179253721537114</v>
       </c>
       <c r="E84">
-        <v>-16.01218350721513</v>
+        <v>-17.83257571661053</v>
       </c>
       <c r="F84">
-        <v>-3.182885092700813</v>
+        <v>-3.149544961472939</v>
       </c>
       <c r="G84">
-        <v>-2.560658467111508</v>
+        <v>-5.824002248083766</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.3633719943664739</v>
       </c>
       <c r="E85">
-        <v>-16.57804350531759</v>
+        <v>-18.15595404549827</v>
       </c>
       <c r="F85">
-        <v>-3.419885148478766</v>
+        <v>-3.447932840370155</v>
       </c>
       <c r="G85">
-        <v>-3.032311890091474</v>
+        <v>-5.554338450636893</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.3757839942771605</v>
       </c>
       <c r="E86">
-        <v>-16.95600805989379</v>
+        <v>-19.59314678436459</v>
       </c>
       <c r="F86">
-        <v>-3.697611059247953</v>
+        <v>-3.82278068728057</v>
       </c>
       <c r="G86">
-        <v>-1.818576510665097</v>
+        <v>-4.4581406800368</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.3484997738497885</v>
       </c>
       <c r="E87">
-        <v>-18.66417109795709</v>
+        <v>-19.88965767696482</v>
       </c>
       <c r="F87">
-        <v>-4.212008992303585</v>
+        <v>-4.140511773400557</v>
       </c>
       <c r="G87">
-        <v>-2.004622548881059</v>
+        <v>-5.078344902454942</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.2775363689148255</v>
       </c>
       <c r="E88">
-        <v>-20.23695087708707</v>
+        <v>-22.70842443693527</v>
       </c>
       <c r="F88">
-        <v>-3.908269859984284</v>
+        <v>-3.873534758050095</v>
       </c>
       <c r="G88">
-        <v>-2.111390953068094</v>
+        <v>-4.754523890531131</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.1596130771569607</v>
       </c>
       <c r="E89">
-        <v>-19.74773077309043</v>
+        <v>-24.31908490113942</v>
       </c>
       <c r="F89">
-        <v>-4.294661835020114</v>
+        <v>-4.465202802438865</v>
       </c>
       <c r="G89">
-        <v>-1.577145045577127</v>
+        <v>-5.671975375829355</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.008214179085255249</v>
       </c>
       <c r="E90">
-        <v>-22.1318727117007</v>
+        <v>-24.50919476845543</v>
       </c>
       <c r="F90">
-        <v>-4.448923726239049</v>
+        <v>-3.957976874356671</v>
       </c>
       <c r="G90">
-        <v>-2.034268484185232</v>
+        <v>-5.329098863781499</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.2249546718398228</v>
       </c>
       <c r="E91">
-        <v>-23.31940162157614</v>
+        <v>-27.48643547632429</v>
       </c>
       <c r="F91">
-        <v>-4.374806381240966</v>
+        <v>-4.571016797737668</v>
       </c>
       <c r="G91">
-        <v>-1.641803310504633</v>
+        <v>-4.761191329247223</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.4906807855965021</v>
       </c>
       <c r="E92">
-        <v>-26.14100320627539</v>
+        <v>-29.59559941624081</v>
       </c>
       <c r="F92">
-        <v>-4.876263558730064</v>
+        <v>-4.602305891276211</v>
       </c>
       <c r="G92">
-        <v>-1.535319613233975</v>
+        <v>-5.324927576402017</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.8028719977180037</v>
       </c>
       <c r="E93">
-        <v>-28.85214625297954</v>
+        <v>-29.72702252465442</v>
       </c>
       <c r="F93">
-        <v>-5.081537142980795</v>
+        <v>-4.75698030946174</v>
       </c>
       <c r="G93">
-        <v>-1.645395252414742</v>
+        <v>-5.123480880337365</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.155727352627161</v>
       </c>
       <c r="E94">
-        <v>-30.0683177609535</v>
+        <v>-32.01448833591193</v>
       </c>
       <c r="F94">
-        <v>-4.899381636207393</v>
+        <v>-5.095502589024592</v>
       </c>
       <c r="G94">
-        <v>-2.280397613393427</v>
+        <v>-5.844266097329646</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.546301087204595</v>
       </c>
       <c r="E95">
-        <v>-33.20050473546882</v>
+        <v>-34.21612145082808</v>
       </c>
       <c r="F95">
-        <v>-5.092962814567609</v>
+        <v>-5.216351452684206</v>
       </c>
       <c r="G95">
-        <v>-2.071747170235321</v>
+        <v>-5.899760772204449</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.967830334756876</v>
       </c>
       <c r="E96">
-        <v>-34.25197564378381</v>
+        <v>-36.37955462325252</v>
       </c>
       <c r="F96">
-        <v>-5.55792212428936</v>
+        <v>-5.245497559751707</v>
       </c>
       <c r="G96">
-        <v>-1.577436373584583</v>
+        <v>-6.076153259627896</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.405798343039308</v>
       </c>
       <c r="E97">
-        <v>-36.23772055309527</v>
+        <v>-37.53203088007159</v>
       </c>
       <c r="F97">
-        <v>-5.509228203250596</v>
+        <v>-5.75231510270432</v>
       </c>
       <c r="G97">
-        <v>-3.17201029075764</v>
+        <v>-6.700638017428316</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.854067544614056</v>
       </c>
       <c r="E98">
-        <v>-38.38143901392732</v>
+        <v>-41.01298054452464</v>
       </c>
       <c r="F98">
-        <v>-5.801089375381155</v>
+        <v>-5.63080188838766</v>
       </c>
       <c r="G98">
-        <v>-3.203102934462474</v>
+        <v>-6.615328569426837</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.286018824430128</v>
       </c>
       <c r="E99">
-        <v>-41.26054316157596</v>
+        <v>-41.66516231416131</v>
       </c>
       <c r="F99">
-        <v>-5.777072519271789</v>
+        <v>-5.9106144566445</v>
       </c>
       <c r="G99">
-        <v>-3.848699041166827</v>
+        <v>-6.726317919176442</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.700790879898076</v>
       </c>
       <c r="E100">
-        <v>-43.22524651641079</v>
+        <v>-44.20310028702009</v>
       </c>
       <c r="F100">
-        <v>-5.985593303741494</v>
+        <v>-5.852309816998456</v>
       </c>
       <c r="G100">
-        <v>-4.610882630127693</v>
+        <v>-7.735981339925527</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.060188903297441</v>
       </c>
       <c r="E101">
-        <v>-44.93616739514476</v>
+        <v>-47.89274694035363</v>
       </c>
       <c r="F101">
-        <v>-6.324720291508389</v>
+        <v>-6.113266258065371</v>
       </c>
       <c r="G101">
-        <v>-5.279159284321593</v>
+        <v>-8.049946857778927</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.387654023848264</v>
       </c>
       <c r="E102">
-        <v>-46.64269791832829</v>
+        <v>-49.32097669704027</v>
       </c>
       <c r="F102">
-        <v>-6.17527121489972</v>
+        <v>-6.212613189050519</v>
       </c>
       <c r="G102">
-        <v>-6.747809980817391</v>
+        <v>-8.198474483398329</v>
       </c>
     </row>
   </sheetData>
